--- a/students/بیگ محمدیcon2.2.xlsx
+++ b/students/بیگ محمدیcon2.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCD360C-BD23-43EF-9D49-A4F3E99E1342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,12 +145,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -200,11 +201,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,23 +477,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.85546875" customWidth="1"/>
+    <col min="7" max="7" width="41.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>111200</v>
       </c>
@@ -535,7 +535,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>10975</v>
       </c>
@@ -558,7 +558,7 @@
         <v>33744048</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>111231</v>
       </c>
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>111188</v>
       </c>
@@ -602,7 +602,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>111404</v>
       </c>
@@ -623,7 +623,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>10818</v>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>10840</v>
       </c>
@@ -657,12 +657,15 @@
       <c r="D8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="E8" s="1">
+        <v>9127416508</v>
+      </c>
+      <c r="F8" s="1">
+        <v>9197506386</v>
+      </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>10814</v>
       </c>
@@ -682,9 +685,8 @@
         <v>9391867502</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>111557</v>
       </c>
@@ -704,9 +706,8 @@
         <v>9940081526</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10936</v>
       </c>
@@ -727,7 +728,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10825</v>
       </c>
@@ -748,74 +749,80 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>111490</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2">
         <v>9901175168</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>9191448900</v>
       </c>
       <c r="G13">
         <v>9964946820</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>111488</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2">
         <v>9211104907</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>9192775142</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>111489</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2">
+        <v>9211104907</v>
+      </c>
+      <c r="F15" s="2">
+        <v>9192775142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>111126</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E16">
@@ -823,16 +830,16 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>111142</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E17">
@@ -846,13 +853,13 @@
       <c r="A18">
         <v>111670</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E18">
